--- a/Procedimento y campos lectores.xlsx
+++ b/Procedimento y campos lectores.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>J</t>
   </si>
@@ -153,6 +153,422 @@
   </si>
   <si>
     <r>
+      <t>Creador, A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">♠, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♣</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Creador, A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">♠, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A♣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> invitada</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Creador, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> invitada</t>
+    </r>
+  </si>
+  <si>
+    <t>A, K</t>
+  </si>
+  <si>
+    <t>Propietario, futuro propietario</t>
+  </si>
+  <si>
+    <t>Miembros</t>
+  </si>
+  <si>
+    <t>Quien aprueba</t>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♠</t>
+    </r>
+  </si>
+  <si>
+    <t>A♦</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A♣,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (si la invitacion contiene ♥)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>♦</t>
+    </r>
+  </si>
+  <si>
+    <t>Quien puede crear</t>
+  </si>
+  <si>
+    <t>A,K</t>
+  </si>
+  <si>
+    <t>Servidor</t>
+  </si>
+  <si>
+    <t>Lectores antes de aprobar</t>
+  </si>
+  <si>
+    <t>Lectores despues de aprobar</t>
+  </si>
+  <si>
+    <t>Excepciones al publicar en News</t>
+  </si>
+  <si>
+    <t>Si hay J♠ o J♣ en news, TODOS</t>
+  </si>
+  <si>
+    <t>Si esta en News, TODOS</t>
+  </si>
+  <si>
+    <t>Quien envia</t>
+  </si>
+  <si>
+    <t>A♣</t>
+  </si>
+  <si>
+    <t>Propietario</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Creador, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>Creador,</t>
     </r>
     <r>
@@ -193,373 +609,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Creador, A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">♠, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♣</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Creador, A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">♠, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A♣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> invitada</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Creador, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> invitada</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Creador, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♣</t>
-    </r>
-  </si>
-  <si>
-    <t>A, K</t>
-  </si>
-  <si>
-    <t>Propietario, futuro propietario</t>
-  </si>
-  <si>
-    <t>Miembros</t>
-  </si>
-  <si>
-    <t>Quien aprueba</t>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♠</t>
-    </r>
-  </si>
-  <si>
-    <t>A♦</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A♣,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (si la invitacion contiene ♥)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -569,59 +624,16 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>♦</t>
-    </r>
-  </si>
-  <si>
-    <t>Quien puede crear</t>
-  </si>
-  <si>
-    <t>A,K</t>
-  </si>
-  <si>
-    <t>Servidor</t>
-  </si>
-  <si>
-    <t>Lectores antes de aprobar</t>
-  </si>
-  <si>
-    <t>Lectores despues de aprobar</t>
-  </si>
-  <si>
-    <t>Excepciones al publicar en News</t>
-  </si>
-  <si>
-    <t>Si hay J♠ o J♣ en news, TODOS</t>
-  </si>
-  <si>
-    <t>Si esta en News, TODOS</t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K♦</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A♠ </t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
@@ -1016,28 +1028,32 @@
     <col min="4" max="4" width="31.140625" customWidth="1"/>
     <col min="5" max="5" width="35.42578125" customWidth="1"/>
     <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1">
+    <row r="1" spans="1:8" s="2" customFormat="1">
       <c r="A1" s="5"/>
       <c r="C1" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75">
+    </row>
+    <row r="2" spans="1:8" ht="18.75">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1061,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1057,10 +1073,13 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1068,13 +1087,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -1082,8 +1101,11 @@
       <c r="G3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75">
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -1091,13 +1113,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
@@ -1105,13 +1127,16 @@
       <c r="G4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75">
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18.75">
       <c r="B5" s="1"/>
       <c r="C5" s="7"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:7" ht="18.75">
+    <row r="6" spans="1:8" ht="18.75">
       <c r="A6" s="5" t="s">
         <v>1</v>
       </c>
@@ -1119,19 +1144,22 @@
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75">
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75">
       <c r="A7" s="5" t="s">
         <v>1</v>
       </c>
@@ -1139,23 +1167,26 @@
         <v>7</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="18.75">
+    <row r="9" spans="1:8" ht="18.75">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
@@ -1163,19 +1194,22 @@
         <v>4</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75">
       <c r="A10" s="5" t="s">
         <v>2</v>
       </c>
@@ -1183,19 +1217,22 @@
         <v>5</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75">
       <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
@@ -1203,19 +1240,22 @@
         <v>6</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18.75">
       <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
@@ -1223,23 +1263,26 @@
         <v>7</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75">
       <c r="B13" s="1"/>
       <c r="C13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="18.75">
+    <row r="14" spans="1:8" ht="18.75">
       <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
@@ -1247,16 +1290,19 @@
         <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75">
       <c r="A15" s="5" t="s">
         <v>3</v>
       </c>
@@ -1264,16 +1310,19 @@
         <v>5</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18.75">
       <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
@@ -1281,16 +1330,19 @@
         <v>6</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75">
       <c r="A17" s="5" t="s">
         <v>3</v>
       </c>
@@ -1298,13 +1350,16 @@
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
